--- a/JsonConverter/ExcelFiles/GameConstant.xlsx
+++ b/JsonConverter/ExcelFiles/GameConstant.xlsx
@@ -44,7 +44,7 @@
     <t>float</t>
   </si>
   <si>
-    <t>Name</t>
+    <t>Id</t>
   </si>
   <si>
     <t>Value</t>

--- a/JsonConverter/ExcelFiles/GameConstant.xlsx
+++ b/JsonConverter/ExcelFiles/GameConstant.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9000"/>
+    <workbookView windowWidth="13128" windowHeight="5856"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="32">
   <si>
     <t>이름</t>
   </si>
@@ -69,6 +69,18 @@
   </si>
   <si>
     <t>과열 시 부스터 사용 금지 시간(초)</t>
+  </si>
+  <si>
+    <t>SHIP_ACCELERATION</t>
+  </si>
+  <si>
+    <t>우주선 기본 가속력</t>
+  </si>
+  <si>
+    <t>SHIP_BOOST_ACCELERATION</t>
+  </si>
+  <si>
+    <t>부스터 기본 가속력</t>
   </si>
   <si>
     <t>STATION_DOCKING_RANGE</t>
@@ -1274,7 +1286,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="28.8888888888889" customWidth="1"/>
@@ -1377,8 +1389,8 @@
       <c r="A8" t="s">
         <v>16</v>
       </c>
-      <c r="B8" s="3">
-        <v>0.2</v>
+      <c r="B8">
+        <v>20</v>
       </c>
       <c r="C8" t="s">
         <v>17</v>
@@ -1389,18 +1401,17 @@
         <v>18</v>
       </c>
       <c r="B9">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C9" t="s">
         <v>19</v>
       </c>
-      <c r="H9" s="4"/>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" t="s">
         <v>20</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="3">
         <v>0.2</v>
       </c>
       <c r="C10" t="s">
@@ -1417,13 +1428,14 @@
       <c r="C11" t="s">
         <v>23</v>
       </c>
+      <c r="H11" s="4"/>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" t="s">
         <v>24</v>
       </c>
       <c r="B12">
-        <v>100</v>
+        <v>0.2</v>
       </c>
       <c r="C12" t="s">
         <v>25</v>
@@ -1441,7 +1453,29 @@
       </c>
     </row>
     <row r="14" spans="1:10">
-      <c r="C14" s="3"/>
+      <c r="A14" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14">
+        <v>100</v>
+      </c>
+      <c r="C14" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" t="s">
+        <v>30</v>
+      </c>
+      <c r="B15">
+        <v>10</v>
+      </c>
+      <c r="C15" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="C16" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/JsonConverter/ExcelFiles/GameConstant.xlsx
+++ b/JsonConverter/ExcelFiles/GameConstant.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="13128" windowHeight="5856"/>
+    <workbookView windowWidth="13272" windowHeight="5856"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="40">
   <si>
     <t>이름</t>
   </si>
@@ -93,6 +93,30 @@
   </si>
   <si>
     <t>정거장 상호작용 가능 속도</t>
+  </si>
+  <si>
+    <t>PROSPERITY_CHANGE_RATE</t>
+  </si>
+  <si>
+    <t>번영도 변화 조정계수</t>
+  </si>
+  <si>
+    <t>PROSPERITY_INCREASE_MAX</t>
+  </si>
+  <si>
+    <t>사이클당 번영도 최대 증가폭</t>
+  </si>
+  <si>
+    <t>POPULATION_CHANGE_RATE</t>
+  </si>
+  <si>
+    <t>인구 변화 조정계수</t>
+  </si>
+  <si>
+    <t>POPULATION_INCREASE_MAX</t>
+  </si>
+  <si>
+    <t>사이클당 인구 최대 증가폭 비율 (BasePop 기준)</t>
   </si>
   <si>
     <t>PLANET_GAMEOVER_TIME</t>
@@ -1286,7 +1310,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:J20"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="28.8888888888889" customWidth="1"/>
@@ -1423,19 +1447,18 @@
         <v>22</v>
       </c>
       <c r="B11">
-        <v>10</v>
+        <v>0.15</v>
       </c>
       <c r="C11" t="s">
         <v>23</v>
       </c>
-      <c r="H11" s="4"/>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" t="s">
         <v>24</v>
       </c>
       <c r="B12">
-        <v>0.2</v>
+        <v>20</v>
       </c>
       <c r="C12" t="s">
         <v>25</v>
@@ -1446,7 +1469,7 @@
         <v>26</v>
       </c>
       <c r="B13">
-        <v>10</v>
+        <v>0.1</v>
       </c>
       <c r="C13" t="s">
         <v>27</v>
@@ -1457,7 +1480,7 @@
         <v>28</v>
       </c>
       <c r="B14">
-        <v>100</v>
+        <v>0.2</v>
       </c>
       <c r="C14" t="s">
         <v>29</v>
@@ -1473,9 +1496,54 @@
       <c r="C15" t="s">
         <v>31</v>
       </c>
+      <c r="H15" s="4"/>
     </row>
     <row r="16" spans="1:10">
-      <c r="C16" s="3"/>
+      <c r="A16" t="s">
+        <v>32</v>
+      </c>
+      <c r="B16">
+        <v>0.2</v>
+      </c>
+      <c r="C16" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
+        <v>34</v>
+      </c>
+      <c r="B17">
+        <v>10</v>
+      </c>
+      <c r="C17" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" t="s">
+        <v>36</v>
+      </c>
+      <c r="B18">
+        <v>100</v>
+      </c>
+      <c r="C18" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" t="s">
+        <v>38</v>
+      </c>
+      <c r="B19">
+        <v>10</v>
+      </c>
+      <c r="C19" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="C20" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/JsonConverter/ExcelFiles/GameConstant.xlsx
+++ b/JsonConverter/ExcelFiles/GameConstant.xlsx
@@ -1436,7 +1436,7 @@
         <v>20</v>
       </c>
       <c r="B10" s="3">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="C10" t="s">
         <v>21</v>

--- a/JsonConverter/ExcelFiles/GameConstant.xlsx
+++ b/JsonConverter/ExcelFiles/GameConstant.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="13272" windowHeight="5856"/>
+    <workbookView windowWidth="14136" windowHeight="8111"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1503,7 +1503,7 @@
         <v>32</v>
       </c>
       <c r="B16">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="C16" t="s">
         <v>33</v>
@@ -1514,7 +1514,7 @@
         <v>34</v>
       </c>
       <c r="B17">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C17" t="s">
         <v>35</v>

--- a/JsonConverter/ExcelFiles/GameConstant.xlsx
+++ b/JsonConverter/ExcelFiles/GameConstant.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="48">
   <si>
     <t>이름</t>
   </si>
@@ -147,6 +147,30 @@
   </si>
   <si>
     <t>광석과 주괴 제련 비율</t>
+  </si>
+  <si>
+    <t>FOOD_CONSUME_BASE</t>
+  </si>
+  <si>
+    <t>식량 초당 소비량 기본값</t>
+  </si>
+  <si>
+    <t>FOOD_CONSUME_RATE</t>
+  </si>
+  <si>
+    <t>식량 초당 소비량 조절계수</t>
+  </si>
+  <si>
+    <t>ORE_PRODUCE_BASE</t>
+  </si>
+  <si>
+    <t>광석 초당 생산량 기본</t>
+  </si>
+  <si>
+    <t>ORE_PRODUCE_RATE</t>
+  </si>
+  <si>
+    <t>광석 초당 생산량 조절계수</t>
   </si>
 </sst>
 </file>
@@ -1310,7 +1334,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:J23"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="28.8888888888889" customWidth="1"/>
@@ -1543,7 +1567,48 @@
       </c>
     </row>
     <row r="20" spans="1:3">
-      <c r="C20" s="3"/>
+      <c r="A20" t="s">
+        <v>40</v>
+      </c>
+      <c r="B20">
+        <v>0</v>
+      </c>
+      <c r="C20" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" t="s">
+        <v>42</v>
+      </c>
+      <c r="B21">
+        <v>0.0001</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" t="s">
+        <v>44</v>
+      </c>
+      <c r="B22">
+        <v>1</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" t="s">
+        <v>46</v>
+      </c>
+      <c r="B23">
+        <v>2e-5</v>
+      </c>
+      <c r="C23" t="s">
+        <v>47</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/JsonConverter/ExcelFiles/GameConstant.xlsx
+++ b/JsonConverter/ExcelFiles/GameConstant.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="14136" windowHeight="8111"/>
+    <workbookView windowWidth="13776" windowHeight="8400"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1460,7 +1460,7 @@
         <v>20</v>
       </c>
       <c r="B10" s="3">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="C10" t="s">
         <v>21</v>
@@ -1604,7 +1604,7 @@
         <v>46</v>
       </c>
       <c r="B23">
-        <v>2e-5</v>
+        <v>1e-5</v>
       </c>
       <c r="C23" t="s">
         <v>47</v>

--- a/JsonConverter/ExcelFiles/GameConstant.xlsx
+++ b/JsonConverter/ExcelFiles/GameConstant.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="13776" windowHeight="8400"/>
+    <workbookView windowWidth="16524" windowHeight="8400"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="42">
   <si>
     <t>이름</t>
   </si>
@@ -59,12 +59,6 @@
     <t>부스터 사용 시 초당 연료 소모량</t>
   </si>
   <si>
-    <t>FUEL_REGEN_RATE</t>
-  </si>
-  <si>
-    <t>일반 이동/정지 시 초당 연료 회복량</t>
-  </si>
-  <si>
     <t>OVERHEAT_DURATION</t>
   </si>
   <si>
@@ -89,12 +83,6 @@
     <t>정거장 상호작용 가능 거리</t>
   </si>
   <si>
-    <t>STATION_DOCKING_SPEED</t>
-  </si>
-  <si>
-    <t>정거장 상호작용 가능 속도</t>
-  </si>
-  <si>
     <t>PROSPERITY_CHANGE_RATE</t>
   </si>
   <si>
@@ -123,12 +111,6 @@
   </si>
   <si>
     <t>번영도 0일 때 유예 시간</t>
-  </si>
-  <si>
-    <t>CARGO_TRANSFER_INTERVAL</t>
-  </si>
-  <si>
-    <t>기본 화물 적재/하역 속도(초)</t>
   </si>
   <si>
     <t>PLANET_CONSUME_INTERVAL</t>
@@ -1334,7 +1316,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J23"/>
+  <dimension ref="A1:J20"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="28.8888888888889" customWidth="1"/>
@@ -1404,8 +1386,8 @@
       <c r="A5" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="3">
-        <v>20</v>
+      <c r="B5">
+        <v>5</v>
       </c>
       <c r="C5" t="s">
         <v>11</v>
@@ -1427,7 +1409,7 @@
         <v>14</v>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="C7" t="s">
         <v>15</v>
@@ -1438,7 +1420,7 @@
         <v>16</v>
       </c>
       <c r="B8">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="C8" t="s">
         <v>17</v>
@@ -1449,7 +1431,7 @@
         <v>18</v>
       </c>
       <c r="B9">
-        <v>5</v>
+        <v>0.15</v>
       </c>
       <c r="C9" t="s">
         <v>19</v>
@@ -1459,8 +1441,8 @@
       <c r="A10" t="s">
         <v>20</v>
       </c>
-      <c r="B10" s="3">
-        <v>1</v>
+      <c r="B10">
+        <v>20</v>
       </c>
       <c r="C10" t="s">
         <v>21</v>
@@ -1471,7 +1453,7 @@
         <v>22</v>
       </c>
       <c r="B11">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="C11" t="s">
         <v>23</v>
@@ -1482,7 +1464,7 @@
         <v>24</v>
       </c>
       <c r="B12">
-        <v>20</v>
+        <v>0.2</v>
       </c>
       <c r="C12" t="s">
         <v>25</v>
@@ -1493,18 +1475,19 @@
         <v>26</v>
       </c>
       <c r="B13">
-        <v>0.1</v>
+        <v>10</v>
       </c>
       <c r="C13" t="s">
         <v>27</v>
       </c>
+      <c r="H13" s="4"/>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" t="s">
         <v>28</v>
       </c>
       <c r="B14">
-        <v>0.2</v>
+        <v>20</v>
       </c>
       <c r="C14" t="s">
         <v>29</v>
@@ -1515,19 +1498,18 @@
         <v>30</v>
       </c>
       <c r="B15">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="C15" t="s">
         <v>31</v>
       </c>
-      <c r="H15" s="4"/>
     </row>
     <row r="16" spans="1:10">
       <c r="A16" t="s">
         <v>32</v>
       </c>
       <c r="B16">
-        <v>0.1</v>
+        <v>10</v>
       </c>
       <c r="C16" t="s">
         <v>33</v>
@@ -1538,7 +1520,7 @@
         <v>34</v>
       </c>
       <c r="B17">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="C17" t="s">
         <v>35</v>
@@ -1549,9 +1531,9 @@
         <v>36</v>
       </c>
       <c r="B18">
-        <v>100</v>
-      </c>
-      <c r="C18" t="s">
+        <v>0.0001</v>
+      </c>
+      <c r="C18" s="3" t="s">
         <v>37</v>
       </c>
     </row>
@@ -1560,9 +1542,9 @@
         <v>38</v>
       </c>
       <c r="B19">
-        <v>10</v>
-      </c>
-      <c r="C19" t="s">
+        <v>1</v>
+      </c>
+      <c r="C19" s="3" t="s">
         <v>39</v>
       </c>
     </row>
@@ -1571,43 +1553,10 @@
         <v>40</v>
       </c>
       <c r="B20">
-        <v>0</v>
+        <v>1e-5</v>
       </c>
       <c r="C20" t="s">
         <v>41</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="A21" t="s">
-        <v>42</v>
-      </c>
-      <c r="B21">
-        <v>0.0001</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3">
-      <c r="A22" t="s">
-        <v>44</v>
-      </c>
-      <c r="B22">
-        <v>1</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3">
-      <c r="A23" t="s">
-        <v>46</v>
-      </c>
-      <c r="B23">
-        <v>1e-5</v>
-      </c>
-      <c r="C23" t="s">
-        <v>47</v>
       </c>
     </row>
   </sheetData>

--- a/JsonConverter/ExcelFiles/GameConstant.xlsx
+++ b/JsonConverter/ExcelFiles/GameConstant.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="40">
   <si>
     <t>이름</t>
   </si>
@@ -141,12 +141,6 @@
   </si>
   <si>
     <t>식량 초당 소비량 조절계수</t>
-  </si>
-  <si>
-    <t>ORE_PRODUCE_BASE</t>
-  </si>
-  <si>
-    <t>광석 초당 생산량 기본</t>
   </si>
   <si>
     <t>ORE_PRODUCE_RATE</t>
@@ -1316,7 +1310,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="28.8888888888889" customWidth="1"/>
@@ -1531,7 +1525,7 @@
         <v>36</v>
       </c>
       <c r="B18">
-        <v>0.0001</v>
+        <v>5e-5</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>37</v>
@@ -1542,21 +1536,10 @@
         <v>38</v>
       </c>
       <c r="B19">
-        <v>1</v>
-      </c>
-      <c r="C19" s="3" t="s">
+        <v>1e-5</v>
+      </c>
+      <c r="C19" t="s">
         <v>39</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20" t="s">
-        <v>40</v>
-      </c>
-      <c r="B20">
-        <v>1e-5</v>
-      </c>
-      <c r="C20" t="s">
-        <v>41</v>
       </c>
     </row>
   </sheetData>

--- a/JsonConverter/ExcelFiles/GameConstant.xlsx
+++ b/JsonConverter/ExcelFiles/GameConstant.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="16524" windowHeight="8400"/>
+    <workbookView windowWidth="23040" windowHeight="9000"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1536,7 +1536,7 @@
         <v>38</v>
       </c>
       <c r="B19">
-        <v>1e-5</v>
+        <v>3e-5</v>
       </c>
       <c r="C19" t="s">
         <v>39</v>

--- a/JsonConverter/ExcelFiles/GameConstant.xlsx
+++ b/JsonConverter/ExcelFiles/GameConstant.xlsx
@@ -1392,7 +1392,7 @@
         <v>12</v>
       </c>
       <c r="B6">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C6" t="s">
         <v>13</v>
@@ -1403,7 +1403,7 @@
         <v>14</v>
       </c>
       <c r="B7">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C7" t="s">
         <v>15</v>
